--- a/Design-Files/Main-Controller-Board-v1.1.0/Deliverables/BOM/JLCPCB-v1.1.0.xlsx
+++ b/Design-Files/Main-Controller-Board-v1.1.0/Deliverables/BOM/JLCPCB-v1.1.0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iftikhar Ahmed\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\benjamin-rcctledboard-hw\Design-Files\Main-Controller-Board-v1.1.0\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -45,22 +45,22 @@
     <t>220uF</t>
   </si>
   <si>
-    <t>B260A-13-F</t>
+    <t>SS510B</t>
   </si>
   <si>
     <t>SMBJ26CA</t>
   </si>
   <si>
-    <t>BSMD1812-110-33V</t>
-  </si>
-  <si>
-    <t>PJ-051AH</t>
+    <t>BSMD2920-330-30V</t>
+  </si>
+  <si>
+    <t>DC-003A-3.5A-1.3</t>
   </si>
   <si>
     <t>Voltlink Target</t>
   </si>
   <si>
-    <t>S5B-PH-SM4-TB(LF)(SN)</t>
+    <t>S5B-XH-A(LF)(SN)</t>
   </si>
   <si>
     <t>4.7uH</t>
@@ -75,7 +75,7 @@
     <t>BC856B</t>
   </si>
   <si>
-    <t>BUK98150-55A/CUF</t>
+    <t>BUK9832-55A/CUX</t>
   </si>
   <si>
     <t>0R</t>
@@ -153,7 +153,7 @@
     <t>D2</t>
   </si>
   <si>
-    <t>F1, F3</t>
+    <t>F1, F2</t>
   </si>
   <si>
     <t>J1</t>
@@ -237,13 +237,10 @@
     <t>189RV0019</t>
   </si>
   <si>
-    <t>SMA</t>
-  </si>
-  <si>
     <t>SMB Bi Directional</t>
   </si>
   <si>
-    <t>Fuse-1812_</t>
+    <t>Fuse-2920</t>
   </si>
   <si>
     <t>YPRH0703-4R7M</t>
@@ -306,21 +303,24 @@
     <t>C694198</t>
   </si>
   <si>
-    <t>C109094</t>
+    <t>C3011128</t>
   </si>
   <si>
     <t>C5331111</t>
   </si>
   <si>
-    <t>C883150</t>
-  </si>
-  <si>
-    <t>C22359773</t>
+    <t>C22368176</t>
+  </si>
+  <si>
+    <t>C779945</t>
   </si>
   <si>
     <t>C145963</t>
   </si>
   <si>
+    <t>C263757</t>
+  </si>
+  <si>
     <t>C338836</t>
   </si>
   <si>
@@ -333,7 +333,7 @@
     <t>C181144</t>
   </si>
   <si>
-    <t>C458219</t>
+    <t>C458151</t>
   </si>
   <si>
     <t>C106231</t>
@@ -369,10 +369,10 @@
     <t>C5123515</t>
   </si>
   <si>
-    <t>C265104</t>
-  </si>
-  <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>SMB</t>
   </si>
 </sst>
 </file>
@@ -838,7 +838,7 @@
         <v>65</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -852,7 +852,7 @@
         <v>66</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -866,7 +866,7 @@
         <v>67</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -880,7 +880,7 @@
         <v>68</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -894,7 +894,7 @@
         <v>69</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -908,7 +908,7 @@
         <v>68</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -922,7 +922,7 @@
         <v>70</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -936,7 +936,7 @@
         <v>66</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -950,7 +950,7 @@
         <v>66</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -964,7 +964,7 @@
         <v>71</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -978,7 +978,7 @@
         <v>70</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -989,10 +989,10 @@
         <v>42</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1003,10 +1003,10 @@
         <v>43</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1017,10 +1017,10 @@
         <v>44</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1034,7 +1034,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1048,7 +1048,7 @@
         <v>12</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1062,7 +1062,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1073,7 +1073,7 @@
         <v>48</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>100</v>
@@ -1087,7 +1087,7 @@
         <v>49</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>101</v>
@@ -1101,7 +1101,7 @@
         <v>50</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>102</v>
@@ -1115,7 +1115,7 @@
         <v>51</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>103</v>
@@ -1129,7 +1129,7 @@
         <v>52</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>104</v>
@@ -1143,7 +1143,7 @@
         <v>53</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>105</v>
@@ -1157,7 +1157,7 @@
         <v>54</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>106</v>
@@ -1171,7 +1171,7 @@
         <v>55</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>107</v>
@@ -1185,7 +1185,7 @@
         <v>56</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>108</v>
@@ -1199,7 +1199,7 @@
         <v>57</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>109</v>
@@ -1213,10 +1213,10 @@
         <v>58</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1227,7 +1227,7 @@
         <v>59</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>110</v>
@@ -1255,7 +1255,7 @@
         <v>61</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>112</v>
@@ -1269,7 +1269,7 @@
         <v>62</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>113</v>
@@ -1297,7 +1297,7 @@
         <v>64</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>115</v>

--- a/Design-Files/Main-Controller-Board-v1.1.0/Deliverables/BOM/JLCPCB-v1.1.0.xlsx
+++ b/Design-Files/Main-Controller-Board-v1.1.0/Deliverables/BOM/JLCPCB-v1.1.0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\benjamin-rcctledboard-hw\Design-Files\Main-Controller-Board-v1.1.0\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-consultants\benjamin-rcctledboard-hw\Design-Files\Main-Controller-Board-v1.1.0\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -282,9 +282,6 @@
     <t>C441864</t>
   </si>
   <si>
-    <t>C327087</t>
-  </si>
-  <si>
     <t>C2842838</t>
   </si>
   <si>
@@ -373,6 +370,9 @@
   </si>
   <si>
     <t>SMB</t>
+  </si>
+  <si>
+    <t>C91183</t>
   </si>
 </sst>
 </file>
@@ -819,15 +819,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -841,7 +841,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -855,7 +855,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
@@ -869,7 +869,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -883,7 +883,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>1</v>
       </c>
@@ -894,10 +894,10 @@
         <v>69</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
@@ -908,10 +908,10 @@
         <v>68</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>5</v>
       </c>
@@ -922,10 +922,10 @@
         <v>70</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
@@ -936,10 +936,10 @@
         <v>66</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>4</v>
       </c>
@@ -950,10 +950,10 @@
         <v>66</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
@@ -964,10 +964,10 @@
         <v>71</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>5</v>
       </c>
@@ -978,10 +978,10 @@
         <v>70</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>8</v>
       </c>
@@ -989,13 +989,13 @@
         <v>42</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
@@ -1006,10 +1006,10 @@
         <v>72</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
@@ -1020,10 +1020,10 @@
         <v>73</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>11</v>
       </c>
@@ -1034,10 +1034,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>12</v>
       </c>
@@ -1048,10 +1048,10 @@
         <v>12</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>13</v>
       </c>
@@ -1062,10 +1062,10 @@
         <v>13</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>14</v>
       </c>
@@ -1076,10 +1076,10 @@
         <v>74</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>15</v>
       </c>
@@ -1090,10 +1090,10 @@
         <v>75</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>16</v>
       </c>
@@ -1104,10 +1104,10 @@
         <v>76</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>17</v>
       </c>
@@ -1118,10 +1118,10 @@
         <v>76</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>18</v>
       </c>
@@ -1132,10 +1132,10 @@
         <v>77</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>19</v>
       </c>
@@ -1146,10 +1146,10 @@
         <v>78</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>20</v>
       </c>
@@ -1160,10 +1160,10 @@
         <v>79</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>21</v>
       </c>
@@ -1174,10 +1174,10 @@
         <v>78</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>22</v>
       </c>
@@ -1188,10 +1188,10 @@
         <v>78</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>23</v>
       </c>
@@ -1202,10 +1202,10 @@
         <v>78</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>24</v>
       </c>
@@ -1216,10 +1216,10 @@
         <v>80</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>25</v>
       </c>
@@ -1230,10 +1230,10 @@
         <v>78</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>26</v>
       </c>
@@ -1244,10 +1244,10 @@
         <v>26</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>27</v>
       </c>
@@ -1258,10 +1258,10 @@
         <v>81</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>28</v>
       </c>
@@ -1272,10 +1272,10 @@
         <v>77</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>29</v>
       </c>
@@ -1286,10 +1286,10 @@
         <v>29</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>30</v>
       </c>
@@ -1300,7 +1300,7 @@
         <v>82</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
